--- a/DataTables/DetailText/剧情/aaa模板.xlsx
+++ b/DataTables/DetailText/剧情/aaa模板.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10094312\Downloads\DataTables\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10094312\Downloads\Doctor\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{012B0860-FF99-4979-9730-D9C8B3A9FA3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{727515D6-0A40-4B82-B2A5-C9E632D3E163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
   <si>
     <t>StoryID</t>
   </si>
@@ -132,7 +132,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -166,32 +166,32 @@
   </cellStyleXfs>
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -476,126 +476,130 @@
   <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.25" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.375" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="34.25" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="44.875" style="6" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="6"/>
+    <col min="1" max="1" width="8.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="34.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="44.875" style="4" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="7"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="3">
+      <c r="A2" s="5"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="1">
         <v>1</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="4" t="s">
+      <c r="E2" s="1"/>
+      <c r="F2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="3"/>
+      <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="7"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="3">
+      <c r="A3" s="5"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="1">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="4" t="s">
+      <c r="E3" s="1"/>
+      <c r="F3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="3"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="7"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="3">
+      <c r="A4" s="5"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="1">
         <v>3</v>
       </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="4" t="s">
+      <c r="D4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="3"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="7"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="3">
+      <c r="A5" s="5"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="1">
         <v>4</v>
       </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="4" t="s">
+      <c r="D5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="3"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="1"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="7"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="3">
+      <c r="A6" s="5"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="1">
         <v>5</v>
       </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="3"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="1"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/aaa模板.xlsx
+++ b/DataTables/DetailText/剧情/aaa模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10094312\Downloads\Doctor\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{727515D6-0A40-4B82-B2A5-C9E632D3E163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA2F94A4-4377-456D-A8B1-F5F35C651ADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>StoryID</t>
   </si>
@@ -78,7 +78,7 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>res:\\assets\Assets\li_shi_zhen.png</t>
+    <t>res://Assets/Portrait/li_shi_zhen.png</t>
   </si>
 </sst>
 </file>
@@ -483,7 +483,7 @@
     <col min="5" max="5" width="9.375" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.625" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="34.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="44.875" style="4" customWidth="1"/>
+    <col min="8" max="8" width="104.75" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -523,12 +523,8 @@
         <v>6</v>
       </c>
       <c r="E2" s="1"/>
-      <c r="F2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:8">
@@ -544,7 +540,9 @@
       <c r="F3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="2"/>
+      <c r="G3" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:8">

--- a/DataTables/DetailText/剧情/aaa模板.xlsx
+++ b/DataTables/DetailText/剧情/aaa模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10094312\Downloads\Doctor\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA2F94A4-4377-456D-A8B1-F5F35C651ADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4514CC28-616F-49C1-A906-005C25A9D23B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -78,7 +78,8 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>res://Assets/Portrait/li_shi_zhen.png</t>
+    <t>res://Assets/Portrait/StoryNpc/li_shi_zhen/li_shi_zhen.png</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -482,7 +483,7 @@
     <col min="4" max="4" width="10.5" style="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.375" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="34.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="57.25" style="4" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="104.75" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>

--- a/DataTables/DetailText/剧情/aaa模板.xlsx
+++ b/DataTables/DetailText/剧情/aaa模板.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10094312\Downloads\Doctor\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4514CC28-616F-49C1-A906-005C25A9D23B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CC1FFB6-00B5-477B-946A-B3486199BFB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1778" yWindow="1778" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="2" r:id="rId1"/>
@@ -20,17 +20,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -78,19 +67,19 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>res://Assets/Portrait/StoryNpc/li_shi_zhen/li_shi_zhen.png</t>
-    <phoneticPr fontId="2"/>
+    <t>BackgroundPath</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -104,7 +93,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -122,6 +111,13 @@
       <name val="Microsoft YaHei"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -196,7 +192,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -474,21 +470,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="57.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="104.75" style="4" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="8.73046875" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.73046875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="104.73046875" style="4" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -511,10 +508,13 @@
         <v>4</v>
       </c>
       <c r="H1" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:9">
       <c r="A2" s="5"/>
       <c r="B2" s="7"/>
       <c r="C2" s="1">
@@ -526,9 +526,10 @@
       <c r="E2" s="1"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
-      <c r="H2" s="1"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:9">
       <c r="A3" s="5"/>
       <c r="B3" s="7"/>
       <c r="C3" s="1">
@@ -541,12 +542,11 @@
       <c r="F3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="1"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:9">
       <c r="A4" s="5"/>
       <c r="B4" s="7"/>
       <c r="C4" s="1">
@@ -560,9 +560,10 @@
         <v>10</v>
       </c>
       <c r="G4" s="2"/>
-      <c r="H4" s="1"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:9">
       <c r="A5" s="5"/>
       <c r="B5" s="7"/>
       <c r="C5" s="1">
@@ -576,9 +577,10 @@
         <v>11</v>
       </c>
       <c r="G5" s="2"/>
-      <c r="H5" s="1"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:9">
       <c r="A6" s="5"/>
       <c r="B6" s="7"/>
       <c r="C6" s="1">
@@ -588,9 +590,10 @@
       <c r="E6" s="1"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="1"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:9">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="3"/>
@@ -599,6 +602,7 @@
       <c r="F7" s="2"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/aaa模板.xlsx
+++ b/DataTables/DetailText/剧情/aaa模板.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CC1FFB6-00B5-477B-946A-B3486199BFB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0548977C-4E13-4F92-8F63-0464CA792C4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1778" yWindow="1778" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="2" r:id="rId1"/>
@@ -20,12 +20,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
   <si>
     <t>StoryID</t>
   </si>
@@ -69,6 +80,14 @@
   <si>
     <t>BackgroundPath</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>res://Assets/Background/</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>mid</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -79,7 +98,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -93,7 +112,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -114,7 +133,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -161,7 +180,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -190,9 +209,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -473,15 +495,15 @@
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.73046875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="104.73046875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="8.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="104.75" style="4" customWidth="1"/>
     <col min="10" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -526,7 +548,9 @@
       <c r="E2" s="1"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
+      <c r="H2" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="I2" s="1"/>
     </row>
     <row r="3" spans="1:9">
@@ -540,7 +564,7 @@
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
@@ -556,8 +580,8 @@
         <v>7</v>
       </c>
       <c r="E4" s="1"/>
-      <c r="F4" s="2" t="s">
-        <v>10</v>
+      <c r="F4" s="10" t="s">
+        <v>14</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>

--- a/DataTables/DetailText/剧情/aaa模板.xlsx
+++ b/DataTables/DetailText/剧情/aaa模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0548977C-4E13-4F92-8F63-0464CA792C4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EABD2D7C-9F15-4A09-ACBB-7F9A639CA301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
   <si>
     <t>StoryID</t>
   </si>
@@ -87,6 +87,10 @@
   </si>
   <si>
     <t>mid</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Hide</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -492,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="8.75" style="4" bestFit="1" customWidth="1"/>
@@ -502,12 +506,13 @@
     <col min="5" max="5" width="9.375" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.625" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="104.75" style="4" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="4"/>
+    <col min="8" max="8" width="6.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="104.75" style="4" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -529,14 +534,17 @@
       <c r="G1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:10">
       <c r="A2" s="5"/>
       <c r="B2" s="7"/>
       <c r="C2" s="1">
@@ -548,12 +556,13 @@
       <c r="E2" s="1"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="2"/>
+      <c r="I2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:10">
       <c r="A3" s="5"/>
       <c r="B3" s="7"/>
       <c r="C3" s="1">
@@ -568,9 +577,10 @@
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
-      <c r="I3" s="1"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:10">
       <c r="A4" s="5"/>
       <c r="B4" s="7"/>
       <c r="C4" s="1">
@@ -585,9 +595,10 @@
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
-      <c r="I4" s="1"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:10">
       <c r="A5" s="5"/>
       <c r="B5" s="7"/>
       <c r="C5" s="1">
@@ -602,9 +613,10 @@
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
-      <c r="I5" s="1"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:10">
       <c r="A6" s="5"/>
       <c r="B6" s="7"/>
       <c r="C6" s="1">
@@ -615,9 +627,10 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
-      <c r="I6" s="1"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="1"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:10">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="3"/>
@@ -627,6 +640,7 @@
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/aaa模板.xlsx
+++ b/DataTables/DetailText/剧情/aaa模板.xlsx
@@ -1,42 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EABD2D7C-9F15-4A09-ACBB-7F9A639CA301}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ED5BDBB-DCB2-479F-829D-3970456821BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="Story" sheetId="3" r:id="rId1"/>
+    <sheet name="StoryLine" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
   <si>
     <t>StoryID</t>
   </si>
@@ -60,10 +50,6 @@
   </si>
   <si>
     <t>dialogue</t>
-  </si>
-  <si>
-    <t>StoryName</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>PortraitSide</t>
@@ -92,17 +78,84 @@
   <si>
     <t>Hide</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>StoryName</t>
+  </si>
+  <si>
+    <t>TriggerType</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TriggerScene</t>
+  </si>
+  <si>
+    <t>TriggerDay</t>
+  </si>
+  <si>
+    <t>Reputation</t>
+  </si>
+  <si>
+    <t>EntryId</t>
+  </si>
+  <si>
+    <t>NpcID</t>
+  </si>
+  <si>
+    <t>TriggerNpcID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>PlayOnce</t>
+  </si>
+  <si>
+    <t>ReturnScene</t>
+  </si>
+  <si>
+    <t>SortIndex</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>落榜</t>
+  </si>
+  <si>
+    <t>scene_enter</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>clinic</t>
+  </si>
+  <si>
+    <t>night</t>
+  </si>
+  <si>
+    <t>feng_han_biao_shi</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>li_shi_zhen</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>story_npc_cured</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>story_npc_treatment_failed</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -116,7 +169,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -137,13 +190,20 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Noto Sans JP"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -153,6 +213,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -184,7 +256,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -201,12 +273,6 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -216,9 +282,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -495,152 +572,251 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
+  <cols>
+    <col min="1" max="1" width="8.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.46484375" customWidth="1"/>
+    <col min="4" max="4" width="14.1328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.86328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.06640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.59765625" customWidth="1"/>
+    <col min="11" max="11" width="13.53125" customWidth="1"/>
+    <col min="12" max="12" width="10.73046875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="18">
+      <c r="A1" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="18">
+      <c r="A2" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J2" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L2" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="18">
+      <c r="C3" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="18">
+      <c r="C4" s="12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="18">
+      <c r="C5" s="12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="104.75" style="4" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.9296875" style="4" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="8" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="E1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="1"/>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="F1" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" s="9" t="s">
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="H1" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="J1" s="8" t="s">
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="5"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="1">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" s="1"/>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="5"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="1">
-        <v>2</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="1"/>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="5"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="1">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="1"/>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="5"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="1">
-        <v>4</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="1"/>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="5"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="1">
-        <v>5</v>
-      </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="1"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
+      <c r="H6" s="1"/>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
       <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
+      <c r="D7" s="2"/>
       <c r="E7" s="3"/>
-      <c r="F7" s="2"/>
+      <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/aaa模板.xlsx
+++ b/DataTables/DetailText/剧情/aaa模板.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ED5BDBB-DCB2-479F-829D-3970456821BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{042E07F1-2037-4445-A3BC-63462C37F170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
   <si>
     <t>StoryID</t>
   </si>
@@ -145,6 +156,18 @@
   <si>
     <t>story_npc_treatment_failed</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>dim</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>hide</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>normal</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -155,7 +178,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -169,7 +192,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -190,7 +213,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -287,7 +310,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -295,7 +318,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -574,23 +597,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.46484375" customWidth="1"/>
-    <col min="4" max="4" width="14.1328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.86328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.86328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.3984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.06640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.59765625" customWidth="1"/>
-    <col min="11" max="11" width="13.53125" customWidth="1"/>
-    <col min="12" max="12" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5" customWidth="1"/>
+    <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.625" customWidth="1"/>
+    <col min="11" max="11" width="13.5" customWidth="1"/>
+    <col min="12" max="12" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="18">
+    <row r="1" spans="1:12">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -628,7 +651,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="18">
+    <row r="2" spans="1:12">
       <c r="A2" s="5" t="s">
         <v>26</v>
       </c>
@@ -666,7 +689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="18">
+    <row r="3" spans="1:12">
       <c r="C3" s="12" t="s">
         <v>28</v>
       </c>
@@ -674,12 +697,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="18">
+    <row r="4" spans="1:12">
       <c r="C4" s="12" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="18">
+    <row r="5" spans="1:12">
       <c r="C5" s="12" t="s">
         <v>34</v>
       </c>
@@ -695,14 +718,14 @@
   <dimension ref="A1:H7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.9296875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -742,7 +765,9 @@
       <c r="C2" s="1"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="F2" s="8" t="s">
+        <v>35</v>
+      </c>
       <c r="G2" s="2" t="s">
         <v>12</v>
       </c>
@@ -760,7 +785,9 @@
         <v>9</v>
       </c>
       <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
+      <c r="F3" s="8" t="s">
+        <v>36</v>
+      </c>
       <c r="G3" s="2"/>
       <c r="H3" s="1"/>
     </row>
@@ -776,7 +803,9 @@
         <v>13</v>
       </c>
       <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
+      <c r="F4" s="8" t="s">
+        <v>37</v>
+      </c>
       <c r="G4" s="2"/>
       <c r="H4" s="1"/>
     </row>

--- a/DataTables/DetailText/剧情/aaa模板.xlsx
+++ b/DataTables/DetailText/剧情/aaa模板.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{042E07F1-2037-4445-A3BC-63462C37F170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A6D7E5B-A734-4CA5-86F8-9F466C3BD9A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,23 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
   <si>
     <t>StoryID</t>
   </si>
@@ -167,6 +156,13 @@
   </si>
   <si>
     <t>normal</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ClinicNpcPortraitPath</t>
+  </si>
+  <si>
+    <t>res://Assets/Portrait/</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -174,11 +170,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -192,7 +188,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -213,12 +209,20 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Noto Sans JP"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Noto Sans JP"/>
@@ -308,17 +312,17 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -596,24 +600,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5" customWidth="1"/>
-    <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.625" customWidth="1"/>
-    <col min="11" max="11" width="13.5" customWidth="1"/>
-    <col min="12" max="12" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.46484375" customWidth="1"/>
+    <col min="4" max="4" width="14.1328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.9296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.06640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.86328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.19921875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.59765625" customWidth="1"/>
+    <col min="12" max="12" width="13.46484375" customWidth="1"/>
+    <col min="13" max="13" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13" ht="18">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -626,32 +631,35 @@
       <c r="D1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="13" t="s">
         <v>22</v>
       </c>
       <c r="J1" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13" ht="18">
       <c r="A2" s="5" t="s">
         <v>26</v>
       </c>
@@ -679,31 +687,34 @@
       <c r="I2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="J2" s="1" t="b">
+      <c r="J2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="L2" s="1">
+      <c r="M2" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
-      <c r="C3" s="12" t="s">
+    <row r="3" spans="1:13" ht="18">
+      <c r="C3" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="13" t="b">
+      <c r="K3" s="11" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
-      <c r="C4" s="12" t="s">
+    <row r="4" spans="1:13" ht="18">
+      <c r="C4" s="10" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
-      <c r="C5" s="12" t="s">
+    <row r="5" spans="1:13" ht="18">
+      <c r="C5" s="10" t="s">
         <v>34</v>
       </c>
     </row>
@@ -718,14 +729,14 @@
   <dimension ref="A1:H7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>

--- a/DataTables/DetailText/剧情/aaa模板.xlsx
+++ b/DataTables/DetailText/剧情/aaa模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A6D7E5B-A734-4CA5-86F8-9F466C3BD9A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F09A32C5-7BD4-4EB2-AD4D-25EA5868D78E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -162,7 +162,7 @@
     <t>ClinicNpcPortraitPath</t>
   </si>
   <si>
-    <t>res://Assets/Portrait/</t>
+    <t>res://Assets/Portrait/.png</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>

--- a/DataTables/DetailText/剧情/aaa模板.xlsx
+++ b/DataTables/DetailText/剧情/aaa模板.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F09A32C5-7BD4-4EB2-AD4D-25EA5868D78E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9548BA3E-7F28-43F5-8930-2F87E1C6C23C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1710" yWindow="3420" windowWidth="18900" windowHeight="10965" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="41">
   <si>
     <t>StoryID</t>
   </si>
@@ -143,10 +154,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>story_npc_treatment_failed</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>dim</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -163,6 +170,14 @@
   </si>
   <si>
     <t>res://Assets/Portrait/.png</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>story_npc_failed_back</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>story_npc_failed_over</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -174,7 +189,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -188,7 +203,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -209,7 +224,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -283,7 +298,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -320,9 +335,12 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -600,25 +618,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <dimension ref="A1:M6"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.46484375" customWidth="1"/>
-    <col min="4" max="4" width="14.1328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.9296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.06640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.86328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.3984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5" customWidth="1"/>
+    <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.25" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="23" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.59765625" customWidth="1"/>
-    <col min="12" max="12" width="13.46484375" customWidth="1"/>
-    <col min="13" max="13" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.625" customWidth="1"/>
+    <col min="12" max="12" width="13.5" customWidth="1"/>
+    <col min="13" max="13" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18">
+    <row r="1" spans="1:13">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -647,7 +665,7 @@
         <v>22</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K1" s="6" t="s">
         <v>23</v>
@@ -659,7 +677,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="18">
+    <row r="2" spans="1:13">
       <c r="A2" s="5" t="s">
         <v>26</v>
       </c>
@@ -688,7 +706,7 @@
         <v>32</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K2" s="1" t="b">
         <v>1</v>
@@ -700,7 +718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="18">
+    <row r="3" spans="1:13">
       <c r="C3" s="10" t="s">
         <v>28</v>
       </c>
@@ -708,14 +726,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="18">
+    <row r="4" spans="1:13">
       <c r="C4" s="10" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="18">
+    <row r="5" spans="1:13">
       <c r="C5" s="10" t="s">
-        <v>34</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="C6" s="14" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -729,14 +752,14 @@
   <dimension ref="A1:H7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -777,7 +800,7 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>12</v>
@@ -797,7 +820,7 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="1"/>
@@ -815,7 +838,7 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="1"/>

--- a/DataTables/DetailText/剧情/aaa模板.xlsx
+++ b/DataTables/DetailText/剧情/aaa模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9548BA3E-7F28-43F5-8930-2F87E1C6C23C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{166DB211-E577-4E05-9DA1-E1618F66B656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1710" yWindow="3420" windowWidth="18900" windowHeight="10965" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
   <si>
     <t>StoryID</t>
   </si>
@@ -101,9 +101,6 @@
     <t>TriggerScene</t>
   </si>
   <si>
-    <t>TriggerDay</t>
-  </si>
-  <si>
     <t>Reputation</t>
   </si>
   <si>
@@ -178,6 +175,14 @@
   </si>
   <si>
     <t>story_npc_failed_over</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TriggerStoryID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TriggerDay</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -185,7 +190,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -298,7 +303,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -335,8 +340,11 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -618,25 +626,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <dimension ref="A1:N21"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5" customWidth="1"/>
+    <col min="3" max="3" width="21.875" customWidth="1"/>
     <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.625" customWidth="1"/>
-    <col min="12" max="12" width="13.5" customWidth="1"/>
-    <col min="13" max="13" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.625" customWidth="1"/>
+    <col min="13" max="13" width="13.5" customWidth="1"/>
+    <col min="14" max="14" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -650,45 +659,48 @@
         <v>17</v>
       </c>
       <c r="E1" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="G1" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="I1" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="J1" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="K1" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="K1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="M1" s="6" t="s">
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A2" s="5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="5" t="s">
+      <c r="B2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="E2" s="1">
         <v>1</v>
@@ -696,50 +708,100 @@
       <c r="F2" s="1">
         <v>0</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="5"/>
+      <c r="H2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="J2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L2" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="C3" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="14"/>
+      <c r="L3" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="C4" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J2" s="2" t="s">
+      <c r="G4" s="14"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="C5" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="K2" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="M2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="C3" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="K3" s="11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="C4" s="10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="C5" s="10" t="s">
+      <c r="G5" s="14"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="C6" s="10" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="C6" s="14" t="s">
-        <v>40</v>
-      </c>
+      <c r="G6" s="14"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G7" s="14"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G8" s="14"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G9" s="14"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G10" s="14"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G11" s="14"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G12" s="14"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G13" s="14"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G14" s="14"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G15" s="14"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G16" s="14"/>
+    </row>
+    <row r="17" spans="7:7" x14ac:dyDescent="0.4">
+      <c r="G17" s="14"/>
+    </row>
+    <row r="18" spans="7:7" x14ac:dyDescent="0.4">
+      <c r="G18" s="14"/>
+    </row>
+    <row r="19" spans="7:7" x14ac:dyDescent="0.4">
+      <c r="G19" s="14"/>
+    </row>
+    <row r="20" spans="7:7" x14ac:dyDescent="0.4">
+      <c r="G20" s="14"/>
+    </row>
+    <row r="21" spans="7:7" x14ac:dyDescent="0.4">
+      <c r="G21" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -750,7 +812,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
@@ -763,7 +825,7 @@
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -789,7 +851,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -800,14 +862,14 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H2" s="1"/>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -820,12 +882,12 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -838,12 +900,12 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -859,7 +921,7 @@
       <c r="G5" s="2"/>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -871,7 +933,7 @@
       <c r="G6" s="2"/>
       <c r="H6" s="1"/>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>

--- a/DataTables/DetailText/剧情/aaa模板.xlsx
+++ b/DataTables/DetailText/剧情/aaa模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{166DB211-E577-4E05-9DA1-E1618F66B656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78932F65-B2CB-447A-B468-CFD6B5EBACC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="44">
   <si>
     <t>StoryID</t>
   </si>
@@ -183,6 +183,14 @@
   </si>
   <si>
     <t>TriggerDay</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TriggerCureCount</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>005_01</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -250,7 +258,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -272,6 +280,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -303,7 +317,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -340,11 +354,17 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -626,26 +646,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.875" customWidth="1"/>
-    <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.625" customWidth="1"/>
-    <col min="13" max="13" width="13.5" customWidth="1"/>
-    <col min="14" max="14" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="25.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5" customWidth="1"/>
+    <col min="15" max="15" width="14.25" customWidth="1"/>
+    <col min="16" max="16" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -658,38 +680,43 @@
       <c r="D1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="G1" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="H1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="I1" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="J1" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="K1" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N1" s="6" t="s">
+      <c r="Q1" s="16" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
         <v>25</v>
       </c>
@@ -702,106 +729,108 @@
       <c r="D2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="1">
         <v>1</v>
       </c>
-      <c r="F2" s="1">
+      <c r="G2" s="1">
         <v>0</v>
       </c>
-      <c r="G2" s="5"/>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="L2" s="1" t="b">
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N2" s="1">
+      <c r="Q2" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
       <c r="C3" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="14"/>
-      <c r="L3" s="11" t="b">
+      <c r="H3" s="14"/>
+      <c r="P3" s="11" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
       <c r="C4" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="14"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="H4" s="14"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
       <c r="C5" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="14"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="H5" s="14"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
       <c r="C6" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="14"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G7" s="14"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G8" s="14"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G9" s="14"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G10" s="14"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G11" s="14"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G12" s="14"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G13" s="14"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G14" s="14"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G15" s="14"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G16" s="14"/>
-    </row>
-    <row r="17" spans="7:7" x14ac:dyDescent="0.4">
-      <c r="G17" s="14"/>
-    </row>
-    <row r="18" spans="7:7" x14ac:dyDescent="0.4">
-      <c r="G18" s="14"/>
-    </row>
-    <row r="19" spans="7:7" x14ac:dyDescent="0.4">
-      <c r="G19" s="14"/>
-    </row>
-    <row r="20" spans="7:7" x14ac:dyDescent="0.4">
-      <c r="G20" s="14"/>
-    </row>
-    <row r="21" spans="7:7" x14ac:dyDescent="0.4">
-      <c r="G21" s="15"/>
+      <c r="H6" s="14"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="H7" s="14"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="H8" s="14"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="H9" s="14"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="H10" s="14"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="H11" s="14"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="H12" s="14"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="H13" s="14"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="H14" s="14"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="H15" s="14"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="H16" s="14"/>
+    </row>
+    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H17" s="14"/>
+    </row>
+    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H18" s="14"/>
+    </row>
+    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H19" s="14"/>
+    </row>
+    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H20" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/aaa模板.xlsx
+++ b/DataTables/DetailText/剧情/aaa模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78932F65-B2CB-447A-B468-CFD6B5EBACC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A57ED08F-216A-45B9-927B-74B4FE9951C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/DataTables/DetailText/剧情/aaa模板.xlsx
+++ b/DataTables/DetailText/剧情/aaa模板.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A57ED08F-216A-45B9-927B-74B4FE9951C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{656D4826-B1DC-43B0-A8A2-3030F8531E47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4237" yWindow="4057" windowWidth="21601" windowHeight="11423" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,23 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="45">
   <si>
     <t>StoryID</t>
   </si>
@@ -191,6 +180,10 @@
   </si>
   <si>
     <t>005_01</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>story_npc_failed_retry</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -198,11 +191,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -216,7 +209,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -237,7 +230,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -317,7 +310,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -366,9 +359,12 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -647,27 +643,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:Q20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="25.125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5" customWidth="1"/>
-    <col min="15" max="15" width="14.25" customWidth="1"/>
-    <col min="16" max="16" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.59765625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="25.1328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.46484375" customWidth="1"/>
+    <col min="15" max="15" width="14.265625" customWidth="1"/>
+    <col min="16" max="16" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -716,7 +712,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" ht="18.75">
       <c r="A2" s="5" t="s">
         <v>25</v>
       </c>
@@ -763,7 +759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17">
       <c r="C3" s="10" t="s">
         <v>27</v>
       </c>
@@ -772,64 +768,67 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" ht="18.75">
       <c r="C4" s="10" t="s">
         <v>32</v>
       </c>
       <c r="H4" s="14"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="C5" s="10" t="s">
+    <row r="5" spans="1:17">
+      <c r="C5" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="H5" s="14"/>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="C6" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="14"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="C6" s="10" t="s">
+      <c r="H6" s="14"/>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="C7" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="H6" s="14"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
       <c r="H7" s="14"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" ht="18.75">
       <c r="H8" s="14"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" ht="18.75">
       <c r="H9" s="14"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" ht="18.75">
       <c r="H10" s="14"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" ht="18.75">
       <c r="H11" s="14"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" ht="18.75">
       <c r="H12" s="14"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" ht="18.75">
       <c r="H13" s="14"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" ht="18.75">
       <c r="H14" s="14"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" ht="18.75">
       <c r="H15" s="14"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" ht="18.75">
       <c r="H16" s="14"/>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="8:8" ht="18.75">
       <c r="H17" s="14"/>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="8:8" ht="18.75">
       <c r="H18" s="14"/>
     </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="8:8" ht="18.75">
       <c r="H19" s="14"/>
     </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="8:8">
       <c r="H20" s="14"/>
     </row>
   </sheetData>
@@ -841,20 +840,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -880,7 +879,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -898,7 +897,7 @@
       </c>
       <c r="H2" s="1"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -916,7 +915,7 @@
       <c r="G3" s="2"/>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -934,7 +933,7 @@
       <c r="G4" s="2"/>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -950,7 +949,7 @@
       <c r="G5" s="2"/>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -962,7 +961,7 @@
       <c r="G6" s="2"/>
       <c r="H6" s="1"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>

--- a/DataTables/DetailText/剧情/aaa模板.xlsx
+++ b/DataTables/DetailText/剧情/aaa模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{656D4826-B1DC-43B0-A8A2-3030F8531E47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BA73F9F-4235-4126-8DC2-F176718867B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4237" yWindow="4057" windowWidth="21601" windowHeight="11423" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-83" yWindow="0" windowWidth="14566" windowHeight="15563" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="50">
   <si>
     <t>StoryID</t>
   </si>
@@ -90,12 +90,6 @@
     <t>TriggerScene</t>
   </si>
   <si>
-    <t>Reputation</t>
-  </si>
-  <si>
-    <t>EntryId</t>
-  </si>
-  <si>
     <t>NpcID</t>
   </si>
   <si>
@@ -128,10 +122,6 @@
     <t>night</t>
   </si>
   <si>
-    <t>feng_han_biao_shi</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>li_shi_zhen</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -184,6 +174,38 @@
   </si>
   <si>
     <t>story_npc_failed_retry</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Reputation</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Experience</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>名望</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>心得</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>第几次治疗</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TriggerReputation</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TriggerEntryId</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>风寒表实证</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -310,7 +332,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -357,9 +379,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -650,15 +669,16 @@
     <col min="3" max="3" width="22.3984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.59765625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.265625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="25.1328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.46484375" customWidth="1"/>
-    <col min="15" max="15" width="14.265625" customWidth="1"/>
+    <col min="13" max="13" width="24.86328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.06640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="10.73046875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
@@ -677,56 +697,60 @@
         <v>17</v>
       </c>
       <c r="E1" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="L1" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="M1" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="N1" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="O1" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="P1" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q1" s="16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="I1" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="J1" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K1" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="L1" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="M1" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q1" s="16" t="s">
+      <c r="B2" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" ht="18.75">
-      <c r="A2" s="5" t="s">
+      <c r="C2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="F2" s="1">
         <v>1</v>
@@ -735,23 +759,29 @@
         <v>0</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L2" s="1"/>
+        <v>28</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="M2" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
+        <v>34</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="P2" s="1" t="b">
         <v>1</v>
       </c>
@@ -761,71 +791,71 @@
     </row>
     <row r="3" spans="1:17">
       <c r="C3" s="10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H3" s="14"/>
       <c r="P3" s="11" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="18.75">
+    <row r="4" spans="1:17">
       <c r="C4" s="10" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="H4" s="14"/>
     </row>
     <row r="5" spans="1:17">
-      <c r="C5" s="18" t="s">
-        <v>44</v>
+      <c r="C5" s="10" t="s">
+        <v>41</v>
       </c>
       <c r="H5" s="14"/>
     </row>
     <row r="6" spans="1:17">
       <c r="C6" s="10" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H6" s="14"/>
     </row>
     <row r="7" spans="1:17">
       <c r="C7" s="10" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H7" s="14"/>
     </row>
-    <row r="8" spans="1:17" ht="18.75">
+    <row r="8" spans="1:17">
       <c r="H8" s="14"/>
     </row>
-    <row r="9" spans="1:17" ht="18.75">
+    <row r="9" spans="1:17">
       <c r="H9" s="14"/>
     </row>
-    <row r="10" spans="1:17" ht="18.75">
+    <row r="10" spans="1:17">
       <c r="H10" s="14"/>
     </row>
-    <row r="11" spans="1:17" ht="18.75">
+    <row r="11" spans="1:17">
       <c r="H11" s="14"/>
     </row>
-    <row r="12" spans="1:17" ht="18.75">
+    <row r="12" spans="1:17">
       <c r="H12" s="14"/>
     </row>
-    <row r="13" spans="1:17" ht="18.75">
+    <row r="13" spans="1:17">
       <c r="H13" s="14"/>
     </row>
-    <row r="14" spans="1:17" ht="18.75">
+    <row r="14" spans="1:17">
       <c r="H14" s="14"/>
     </row>
-    <row r="15" spans="1:17" ht="18.75">
+    <row r="15" spans="1:17">
       <c r="H15" s="14"/>
     </row>
-    <row r="16" spans="1:17" ht="18.75">
+    <row r="16" spans="1:17">
       <c r="H16" s="14"/>
     </row>
-    <row r="17" spans="8:8" ht="18.75">
+    <row r="17" spans="8:8">
       <c r="H17" s="14"/>
     </row>
-    <row r="18" spans="8:8" ht="18.75">
+    <row r="18" spans="8:8">
       <c r="H18" s="14"/>
     </row>
-    <row r="19" spans="8:8" ht="18.75">
+    <row r="19" spans="8:8">
       <c r="H19" s="14"/>
     </row>
     <row r="20" spans="8:8">
@@ -890,7 +920,7 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="8" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>12</v>
@@ -910,7 +940,7 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="1"/>
@@ -928,7 +958,7 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="1"/>

--- a/DataTables/DetailText/剧情/aaa模板.xlsx
+++ b/DataTables/DetailText/剧情/aaa模板.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BA73F9F-4235-4126-8DC2-F176718867B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5EAAF06-4961-43FB-B80C-34327C99F4D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="14566" windowHeight="15563" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="48">
   <si>
     <t>StoryID</t>
   </si>
@@ -165,10 +176,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>TriggerCureCount</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>005_01</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -190,10 +197,6 @@
   </si>
   <si>
     <t>心得</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>第几次治疗</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -213,11 +216,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -231,7 +234,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -252,7 +255,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -383,7 +386,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -661,29 +664,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:Q20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <dimension ref="A1:P20"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="24.86328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.06640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -703,13 +705,13 @@
         <v>38</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H1" s="12" t="s">
         <v>37</v>
       </c>
       <c r="I1" s="12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J1" s="13" t="s">
         <v>18</v>
@@ -717,26 +719,23 @@
       <c r="K1" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="13" t="s">
-        <v>39</v>
+      <c r="L1" s="15" t="s">
+        <v>33</v>
       </c>
       <c r="M1" s="15" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="N1" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="O1" s="15" t="s">
-        <v>43</v>
+      <c r="O1" s="16" t="s">
+        <v>20</v>
       </c>
       <c r="P1" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q1" s="16" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
         <v>23</v>
       </c>
@@ -759,10 +758,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>28</v>
@@ -770,95 +769,92 @@
       <c r="K2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>46</v>
+      <c r="L2" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="O2" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="P2" s="1" t="b">
+      <c r="O2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="P2" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C3" s="10" t="s">
         <v>25</v>
       </c>
       <c r="H3" s="14"/>
-      <c r="P3" s="11" t="b">
+      <c r="O3" s="11" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C4" s="10" t="s">
         <v>29</v>
       </c>
       <c r="H4" s="14"/>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C5" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H5" s="14"/>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C6" s="10" t="s">
         <v>35</v>
       </c>
       <c r="H6" s="14"/>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C7" s="10" t="s">
         <v>36</v>
       </c>
       <c r="H7" s="14"/>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H8" s="14"/>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H9" s="14"/>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H10" s="14"/>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H11" s="14"/>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H12" s="14"/>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H13" s="14"/>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H14" s="14"/>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H15" s="14"/>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H16" s="14"/>
     </row>
-    <row r="17" spans="8:8">
+    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H17" s="14"/>
     </row>
-    <row r="18" spans="8:8">
+    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H18" s="14"/>
     </row>
-    <row r="19" spans="8:8">
+    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H19" s="14"/>
     </row>
-    <row r="20" spans="8:8">
+    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H20" s="14"/>
     </row>
   </sheetData>
@@ -870,20 +866,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -909,7 +905,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -927,7 +923,7 @@
       </c>
       <c r="H2" s="1"/>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -945,7 +941,7 @@
       <c r="G3" s="2"/>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -963,7 +959,7 @@
       <c r="G4" s="2"/>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -979,7 +975,7 @@
       <c r="G5" s="2"/>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -991,7 +987,7 @@
       <c r="G6" s="2"/>
       <c r="H6" s="1"/>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>

--- a/DataTables/DetailText/剧情/aaa模板.xlsx
+++ b/DataTables/DetailText/剧情/aaa模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5EAAF06-4961-43FB-B80C-34327C99F4D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{159AABDB-8A49-4A52-92E6-6E4459100F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/DataTables/DetailText/剧情/aaa模板.xlsx
+++ b/DataTables/DetailText/剧情/aaa模板.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{159AABDB-8A49-4A52-92E6-6E4459100F6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A145FA33-FC98-48F4-B288-23A043980AD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4642" yWindow="3188" windowWidth="21601" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,17 +21,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -104,10 +93,6 @@
     <t>NpcID</t>
   </si>
   <si>
-    <t>TriggerNpcID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>PlayOnce</t>
   </si>
   <si>
@@ -210,17 +195,21 @@
   <si>
     <t>风寒表实证</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Disease</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -234,7 +223,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -255,7 +244,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -386,7 +375,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -665,27 +654,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.86328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -699,57 +688,57 @@
         <v>17</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G1" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1" s="12" t="s">
         <v>45</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1" s="12" t="s">
-        <v>46</v>
       </c>
       <c r="J1" s="13" t="s">
         <v>18</v>
       </c>
       <c r="K1" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="L1" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="M1" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="N1" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="O1" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="M1" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="N1" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="O1" s="16" t="s">
-        <v>20</v>
-      </c>
       <c r="P1" s="16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="5" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A2" s="5" t="s">
+      <c r="B2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="F2" s="1">
         <v>1</v>
@@ -758,25 +747,25 @@
         <v>0</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N2" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="O2" s="1" t="b">
         <v>1</v>
@@ -785,76 +774,76 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16">
       <c r="C3" s="10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H3" s="14"/>
       <c r="O3" s="11" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" ht="18.75">
       <c r="C4" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H4" s="14"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" ht="18.75">
       <c r="C5" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H5" s="14"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" ht="18.75">
       <c r="C6" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="14"/>
+    </row>
+    <row r="7" spans="1:16" ht="18.75">
+      <c r="C7" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="14"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C7" s="10" t="s">
-        <v>36</v>
-      </c>
       <c r="H7" s="14"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" ht="18.75">
       <c r="H8" s="14"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" ht="18.75">
       <c r="H9" s="14"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" ht="18.75">
       <c r="H10" s="14"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" ht="18.75">
       <c r="H11" s="14"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16" ht="18.75">
       <c r="H12" s="14"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" ht="18.75">
       <c r="H13" s="14"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16" ht="18.75">
       <c r="H14" s="14"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" ht="18.75">
       <c r="H15" s="14"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16" ht="18.75">
       <c r="H16" s="14"/>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="8:8" ht="18.75">
       <c r="H17" s="14"/>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="8:8" ht="18.75">
       <c r="H18" s="14"/>
     </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="8:8" ht="18.75">
       <c r="H19" s="14"/>
     </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="8:8">
       <c r="H20" s="14"/>
     </row>
   </sheetData>
@@ -866,20 +855,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -905,7 +894,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -916,14 +905,14 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H2" s="1"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -936,12 +925,12 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -954,12 +943,12 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -975,7 +964,7 @@
       <c r="G5" s="2"/>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -987,7 +976,7 @@
       <c r="G6" s="2"/>
       <c r="H6" s="1"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>

--- a/DataTables/DetailText/剧情/aaa模板.xlsx
+++ b/DataTables/DetailText/剧情/aaa模板.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A145FA33-FC98-48F4-B288-23A043980AD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0CE7878-FCBD-41B2-91A6-F9D0BAEA34D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4642" yWindow="3188" windowWidth="21601" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="49">
   <si>
     <t>StoryID</t>
   </si>
@@ -199,17 +210,20 @@
   <si>
     <t>Disease</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>current_scene</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -223,7 +237,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -244,7 +258,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -324,7 +338,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -373,9 +387,10 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -654,27 +669,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.86328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -724,7 +739,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
         <v>22</v>
       </c>
@@ -774,76 +789,77 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C3" s="10" t="s">
         <v>24</v>
       </c>
       <c r="H3" s="14"/>
+      <c r="L3" s="18"/>
       <c r="O3" s="11" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="18.75">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C4" s="10" t="s">
         <v>28</v>
       </c>
       <c r="H4" s="14"/>
     </row>
-    <row r="5" spans="1:16" ht="18.75">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C5" s="10" t="s">
         <v>39</v>
       </c>
       <c r="H5" s="14"/>
     </row>
-    <row r="6" spans="1:16" ht="18.75">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C6" s="10" t="s">
         <v>34</v>
       </c>
       <c r="H6" s="14"/>
     </row>
-    <row r="7" spans="1:16" ht="18.75">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C7" s="10" t="s">
         <v>35</v>
       </c>
       <c r="H7" s="14"/>
     </row>
-    <row r="8" spans="1:16" ht="18.75">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H8" s="14"/>
     </row>
-    <row r="9" spans="1:16" ht="18.75">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H9" s="14"/>
     </row>
-    <row r="10" spans="1:16" ht="18.75">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H10" s="14"/>
     </row>
-    <row r="11" spans="1:16" ht="18.75">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H11" s="14"/>
     </row>
-    <row r="12" spans="1:16" ht="18.75">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H12" s="14"/>
     </row>
-    <row r="13" spans="1:16" ht="18.75">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H13" s="14"/>
     </row>
-    <row r="14" spans="1:16" ht="18.75">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H14" s="14"/>
     </row>
-    <row r="15" spans="1:16" ht="18.75">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H15" s="14"/>
     </row>
-    <row r="16" spans="1:16" ht="18.75">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H16" s="14"/>
     </row>
-    <row r="17" spans="8:8" ht="18.75">
+    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H17" s="14"/>
     </row>
-    <row r="18" spans="8:8" ht="18.75">
+    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H18" s="14"/>
     </row>
-    <row r="19" spans="8:8" ht="18.75">
+    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H19" s="14"/>
     </row>
-    <row r="20" spans="8:8">
+    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H20" s="14"/>
     </row>
   </sheetData>
@@ -855,20 +871,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -894,7 +910,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -902,7 +918,9 @@
         <v>6</v>
       </c>
       <c r="C2" s="1"/>
-      <c r="D2" s="2"/>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="E2" s="2"/>
       <c r="F2" s="8" t="s">
         <v>29</v>
@@ -912,7 +930,7 @@
       </c>
       <c r="H2" s="1"/>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -927,10 +945,12 @@
       <c r="F3" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="2"/>
+      <c r="G3" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -948,7 +968,7 @@
       <c r="G4" s="2"/>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -956,15 +976,13 @@
         <v>7</v>
       </c>
       <c r="C5" s="1"/>
-      <c r="D5" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="D5" s="2"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -976,7 +994,7 @@
       <c r="G6" s="2"/>
       <c r="H6" s="1"/>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>

--- a/DataTables/DetailText/剧情/aaa模板.xlsx
+++ b/DataTables/DetailText/剧情/aaa模板.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0CE7878-FCBD-41B2-91A6-F9D0BAEA34D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90E2E8A4-80CB-49A7-95A3-30EAF172C148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2708" yWindow="2332" windowWidth="21600" windowHeight="11423" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,23 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="50">
   <si>
     <t>StoryID</t>
   </si>
@@ -213,17 +202,21 @@
   </si>
   <si>
     <t>current_scene</t>
+  </si>
+  <si>
+    <t>night_end</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -237,7 +230,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -258,7 +251,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -390,7 +383,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -669,27 +662,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.86328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -739,7 +732,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" ht="18.75">
       <c r="A2" s="5" t="s">
         <v>22</v>
       </c>
@@ -789,7 +782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16">
       <c r="C3" s="10" t="s">
         <v>24</v>
       </c>
@@ -799,67 +792,70 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" ht="18.75">
       <c r="C4" s="10" t="s">
         <v>28</v>
       </c>
       <c r="H4" s="14"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" ht="18.75">
       <c r="C5" s="10" t="s">
         <v>39</v>
       </c>
       <c r="H5" s="14"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" ht="18.75">
       <c r="C6" s="10" t="s">
         <v>34</v>
       </c>
       <c r="H6" s="14"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" ht="18.75">
       <c r="C7" s="10" t="s">
         <v>35</v>
       </c>
       <c r="H7" s="14"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16">
+      <c r="C8" s="10" t="s">
+        <v>49</v>
+      </c>
       <c r="H8" s="14"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" ht="18.75">
       <c r="H9" s="14"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" ht="18.75">
       <c r="H10" s="14"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" ht="18.75">
       <c r="H11" s="14"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16" ht="18.75">
       <c r="H12" s="14"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" ht="18.75">
       <c r="H13" s="14"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16" ht="18.75">
       <c r="H14" s="14"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" ht="18.75">
       <c r="H15" s="14"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16" ht="18.75">
       <c r="H16" s="14"/>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="8:8" ht="18.75">
       <c r="H17" s="14"/>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="8:8" ht="18.75">
       <c r="H18" s="14"/>
     </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="8:8" ht="18.75">
       <c r="H19" s="14"/>
     </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="8:8">
       <c r="H20" s="14"/>
     </row>
   </sheetData>
@@ -871,20 +867,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -910,7 +906,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -930,7 +926,7 @@
       </c>
       <c r="H2" s="1"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -950,7 +946,7 @@
       </c>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -968,7 +964,7 @@
       <c r="G4" s="2"/>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -982,7 +978,7 @@
       <c r="G5" s="2"/>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -994,7 +990,7 @@
       <c r="G6" s="2"/>
       <c r="H6" s="1"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>

--- a/DataTables/DetailText/剧情/aaa模板.xlsx
+++ b/DataTables/DetailText/剧情/aaa模板.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90E2E8A4-80CB-49A7-95A3-30EAF172C148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D54214BC-FC9F-49A0-A692-082FDD15210B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2708" yWindow="2332" windowWidth="21600" windowHeight="11423" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,6 +21,17 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -212,11 +223,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -230,7 +241,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -251,7 +262,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -383,7 +394,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -662,27 +673,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.86328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -732,7 +743,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="18.75">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
         <v>22</v>
       </c>
@@ -782,7 +793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C3" s="10" t="s">
         <v>24</v>
       </c>
@@ -792,70 +803,70 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="18.75">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C4" s="10" t="s">
         <v>28</v>
       </c>
       <c r="H4" s="14"/>
     </row>
-    <row r="5" spans="1:16" ht="18.75">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C5" s="10" t="s">
         <v>39</v>
       </c>
       <c r="H5" s="14"/>
     </row>
-    <row r="6" spans="1:16" ht="18.75">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C6" s="10" t="s">
         <v>34</v>
       </c>
       <c r="H6" s="14"/>
     </row>
-    <row r="7" spans="1:16" ht="18.75">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C7" s="10" t="s">
         <v>35</v>
       </c>
       <c r="H7" s="14"/>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C8" s="10" t="s">
         <v>49</v>
       </c>
       <c r="H8" s="14"/>
     </row>
-    <row r="9" spans="1:16" ht="18.75">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H9" s="14"/>
     </row>
-    <row r="10" spans="1:16" ht="18.75">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H10" s="14"/>
     </row>
-    <row r="11" spans="1:16" ht="18.75">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H11" s="14"/>
     </row>
-    <row r="12" spans="1:16" ht="18.75">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H12" s="14"/>
     </row>
-    <row r="13" spans="1:16" ht="18.75">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H13" s="14"/>
     </row>
-    <row r="14" spans="1:16" ht="18.75">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H14" s="14"/>
     </row>
-    <row r="15" spans="1:16" ht="18.75">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H15" s="14"/>
     </row>
-    <row r="16" spans="1:16" ht="18.75">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H16" s="14"/>
     </row>
-    <row r="17" spans="8:8" ht="18.75">
+    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H17" s="14"/>
     </row>
-    <row r="18" spans="8:8" ht="18.75">
+    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H18" s="14"/>
     </row>
-    <row r="19" spans="8:8" ht="18.75">
+    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H19" s="14"/>
     </row>
-    <row r="20" spans="8:8">
+    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H20" s="14"/>
     </row>
   </sheetData>
@@ -867,20 +878,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -906,7 +917,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -915,7 +926,7 @@
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="8" t="s">
@@ -926,7 +937,7 @@
       </c>
       <c r="H2" s="1"/>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -935,7 +946,7 @@
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8" t="s">
@@ -946,7 +957,7 @@
       </c>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -964,7 +975,7 @@
       <c r="G4" s="2"/>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -978,7 +989,7 @@
       <c r="G5" s="2"/>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -990,7 +1001,7 @@
       <c r="G6" s="2"/>
       <c r="H6" s="1"/>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>

--- a/DataTables/DetailText/剧情/aaa模板.xlsx
+++ b/DataTables/DetailText/剧情/aaa模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D54214BC-FC9F-49A0-A692-082FDD15210B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E298C1B-D73F-45A9-8A7B-78EA194EE300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="52">
   <si>
     <t>StoryID</t>
   </si>
@@ -216,6 +216,14 @@
   </si>
   <si>
     <t>night_end</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>day_reputation_over</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>day_reputation_below_over</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -677,7 +685,7 @@
   <cols>
     <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
@@ -834,9 +842,15 @@
       <c r="H8" s="14"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="C9" s="10" t="s">
+        <v>50</v>
+      </c>
       <c r="H9" s="14"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="C10" s="10" t="s">
+        <v>51</v>
+      </c>
       <c r="H10" s="14"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.4">

--- a/DataTables/DetailText/剧情/aaa模板.xlsx
+++ b/DataTables/DetailText/剧情/aaa模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E298C1B-D73F-45A9-8A7B-78EA194EE300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{529B0DCD-39CE-4CFD-B5C5-A4D1B66569AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="20490" windowHeight="8025" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="54">
   <si>
     <t>StoryID</t>
   </si>
@@ -224,6 +224,14 @@
   </si>
   <si>
     <t>day_reputation_below_over</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Money</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TriggerMoney</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -231,7 +239,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -288,6 +296,14 @@
       <color theme="1"/>
       <name val="Noto Sans JP"/>
       <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -350,7 +366,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -400,6 +416,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -680,7 +699,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
@@ -689,19 +708,21 @@
     <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5" customWidth="1"/>
+    <col min="8" max="8" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -721,37 +742,43 @@
         <v>37</v>
       </c>
       <c r="G1" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="I1" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="J1" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="K1" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="L1" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="L1" s="15" t="s">
+      <c r="M1" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="N1" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="O1" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="N1" s="15" t="s">
+      <c r="P1" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="O1" s="16" t="s">
+      <c r="Q1" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="P1" s="16" t="s">
+      <c r="R1" s="16" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A2" s="5" t="s">
         <v>22</v>
       </c>
@@ -770,118 +797,121 @@
       <c r="F2" s="1">
         <v>1</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="1"/>
+      <c r="H2" s="1">
         <v>0</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="I2" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2"/>
+      <c r="O2" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O2" s="1" t="b">
+      <c r="Q2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="P2" s="1">
+      <c r="R2" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.4">
       <c r="C3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="14"/>
-      <c r="L3" s="18"/>
-      <c r="O3" s="11" t="b">
+      <c r="I3" s="14"/>
+      <c r="M3" s="18"/>
+      <c r="N3" s="18"/>
+      <c r="Q3" s="11" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.4">
       <c r="C4" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="I4" s="14"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="C5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="14"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C5" s="10" t="s">
+      <c r="I5" s="14"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="C6" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="H5" s="14"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C6" s="10" t="s">
+      <c r="I6" s="14"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="C7" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="H6" s="14"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C7" s="10" t="s">
+      <c r="I7" s="14"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="C8" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="H7" s="14"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C8" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="H8" s="14"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="I8" s="14"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.4">
       <c r="C9" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="H9" s="14"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="I9" s="14"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.4">
       <c r="C10" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="H10" s="14"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H11" s="14"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H12" s="14"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H13" s="14"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H14" s="14"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H15" s="14"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H16" s="14"/>
-    </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H17" s="14"/>
-    </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H18" s="14"/>
-    </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H19" s="14"/>
-    </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H20" s="14"/>
+      <c r="I10" s="14"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="I11" s="14"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="I12" s="14"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="I13" s="14"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="I14" s="14"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="I15" s="14"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="I16" s="14"/>
+    </row>
+    <row r="17" spans="9:9" x14ac:dyDescent="0.4">
+      <c r="I17" s="14"/>
+    </row>
+    <row r="18" spans="9:9" x14ac:dyDescent="0.4">
+      <c r="I18" s="14"/>
+    </row>
+    <row r="19" spans="9:9" x14ac:dyDescent="0.4">
+      <c r="I19" s="14"/>
+    </row>
+    <row r="20" spans="9:9" x14ac:dyDescent="0.4">
+      <c r="I20" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/aaa模板.xlsx
+++ b/DataTables/DetailText/剧情/aaa模板.xlsx
@@ -1,40 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10094312\Downloads\剧情系统重构_修改文件\story_refactor_package\DataTables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25968980-7634-4603-87BB-5BF92CD9710D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A76BB6F-0DAC-40E8-8DFF-C3DF6BD9FC7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-83" yWindow="0" windowWidth="14566" windowHeight="15563" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
     <sheet name="StoryLine" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="38">
   <si>
     <t>LineIndex</t>
   </si>
@@ -90,74 +77,102 @@
     <t>normal</t>
   </si>
   <si>
-    <t>StoryID</t>
-  </si>
-  <si>
-    <t>StoryName</t>
-  </si>
-  <si>
-    <t>ConditionScene</t>
-  </si>
-  <si>
-    <t>ConditionDay</t>
-  </si>
-  <si>
-    <t>ConditionMoneyOp</t>
-  </si>
-  <si>
-    <t>ConditionMoney</t>
-  </si>
-  <si>
-    <t>ConditionReputationOp</t>
-  </si>
-  <si>
-    <t>ConditionReputation</t>
-  </si>
-  <si>
-    <t>ConditionEntryId</t>
-  </si>
-  <si>
-    <t>ConditionStoryID</t>
-  </si>
-  <si>
-    <t>ConditionTreatmentResult</t>
-  </si>
-  <si>
-    <t>ReturnScene</t>
-  </si>
-  <si>
-    <t>EndGame</t>
-  </si>
-  <si>
-    <t>NpcID</t>
-  </si>
-  <si>
-    <t>Disease</t>
-  </si>
-  <si>
-    <t>ClinicNpcPortraitPath</t>
-  </si>
-  <si>
-    <t>Money</t>
-  </si>
-  <si>
-    <t>Reputation</t>
-  </si>
-  <si>
-    <t>Experience</t>
-  </si>
-  <si>
     <t>PlayOnce</t>
   </si>
   <si>
     <t>SortIndex</t>
+  </si>
+  <si>
+    <t>剧情ID</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>剧情名</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>触发天数</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>触发金钱</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>触发名望</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>触发条目</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>触发剧情ID</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>触发治疗结果</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>疾病</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>人物ID</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>人物立绘路径</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>奖励心得</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>触发场景</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>奖励金钱</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>奖励名望</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <t>金</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>钱判定</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>名望判定</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>播放后</t>
+    <phoneticPr fontId="4"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -186,10 +201,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Noto Sans JP"/>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
     </font>
@@ -197,7 +210,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Microsoft YaHei"/>
+      <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
@@ -205,15 +218,16 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
+      <name val="Noto Sans JP"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="6"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Noto Sans JP"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="7">
@@ -291,7 +305,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -329,34 +343,10 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -368,15 +358,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -586,98 +592,89 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:T20"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24" customWidth="1"/>
-    <col min="8" max="8" width="21.625" customWidth="1"/>
-    <col min="9" max="9" width="18.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.875" customWidth="1"/>
-    <col min="11" max="11" width="27" customWidth="1"/>
-    <col min="12" max="12" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="33.125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.25" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.6875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.5625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.0625" customWidth="1"/>
+    <col min="5" max="8" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.9375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.9375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="28.75" customWidth="1"/>
+    <col min="16" max="18" width="8.375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.4375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.5625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:20" s="25" customFormat="1">
+      <c r="A1" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="L1" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="N1" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="O1" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q1" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="R1" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="S1" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="T1" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="F1" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="G1" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="I1" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="J1" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="K1" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="L1" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="M1" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="N1" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="O1" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="P1" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q1" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="R1" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="S1" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="T1" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="U1" s="27" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:20">
       <c r="A2" s="11"/>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -690,244 +687,244 @@
       <c r="J2" s="11"/>
       <c r="K2" s="10"/>
       <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="10"/>
       <c r="O2" s="10"/>
       <c r="P2" s="10"/>
       <c r="Q2" s="10"/>
-      <c r="R2" s="10"/>
-      <c r="S2" s="25"/>
-      <c r="T2" s="25"/>
-      <c r="U2" s="25"/>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="A3" s="23"/>
-      <c r="B3" s="20"/>
+      <c r="R2" s="17"/>
+      <c r="S2" s="17"/>
+      <c r="T2" s="17"/>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="A3" s="15"/>
+      <c r="B3" s="13"/>
       <c r="C3" s="8"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
       <c r="I3" s="9"/>
-      <c r="J3" s="23"/>
-      <c r="K3" s="20"/>
-      <c r="L3" s="20"/>
-      <c r="M3" s="21"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="20"/>
-      <c r="P3" s="20"/>
-      <c r="Q3" s="22"/>
-      <c r="R3" s="20"/>
-      <c r="S3" s="20"/>
-      <c r="T3" s="20"/>
-      <c r="U3" s="20"/>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="A4" s="23"/>
-      <c r="B4" s="20"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="14"/>
+      <c r="Q3" s="13"/>
+      <c r="R3" s="13"/>
+      <c r="S3" s="13"/>
+      <c r="T3" s="13"/>
+    </row>
+    <row r="4" spans="1:20">
+      <c r="A4" s="15"/>
+      <c r="B4" s="13"/>
       <c r="C4" s="8"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
       <c r="I4" s="9"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="20"/>
-      <c r="M4" s="20"/>
-      <c r="N4" s="23"/>
-      <c r="O4" s="20"/>
-      <c r="P4" s="20"/>
-      <c r="Q4" s="20"/>
-      <c r="R4" s="20"/>
-      <c r="S4" s="20"/>
-      <c r="T4" s="20"/>
-      <c r="U4" s="20"/>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="A5" s="23"/>
-      <c r="B5" s="20"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="13"/>
+      <c r="S4" s="13"/>
+      <c r="T4" s="13"/>
+    </row>
+    <row r="5" spans="1:20">
+      <c r="A5" s="15"/>
+      <c r="B5" s="13"/>
       <c r="C5" s="8"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
       <c r="I5" s="9"/>
-      <c r="J5" s="23"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="20"/>
-      <c r="M5" s="20"/>
-      <c r="N5" s="23"/>
-      <c r="O5" s="20"/>
-      <c r="P5" s="20"/>
-      <c r="Q5" s="20"/>
-      <c r="R5" s="20"/>
-      <c r="S5" s="20"/>
-      <c r="T5" s="20"/>
-      <c r="U5" s="20"/>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="A6" s="23"/>
-      <c r="B6" s="20"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13"/>
+      <c r="R5" s="13"/>
+      <c r="S5" s="13"/>
+      <c r="T5" s="13"/>
+    </row>
+    <row r="6" spans="1:20">
+      <c r="A6" s="15"/>
+      <c r="B6" s="13"/>
       <c r="C6" s="8"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
       <c r="I6" s="9"/>
-      <c r="J6" s="23"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="20"/>
-      <c r="M6" s="20"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="20"/>
-      <c r="P6" s="20"/>
-      <c r="Q6" s="20"/>
-      <c r="R6" s="20"/>
-      <c r="S6" s="20"/>
-      <c r="T6" s="20"/>
-      <c r="U6" s="20"/>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="A7" s="23"/>
-      <c r="B7" s="20"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="13"/>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="13"/>
+      <c r="R6" s="13"/>
+      <c r="S6" s="13"/>
+      <c r="T6" s="13"/>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="A7" s="15"/>
+      <c r="B7" s="13"/>
       <c r="C7" s="8"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="20"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
       <c r="I7" s="9"/>
-      <c r="J7" s="23"/>
-      <c r="K7" s="20"/>
-      <c r="L7" s="20"/>
-      <c r="M7" s="20"/>
-      <c r="N7" s="23"/>
-      <c r="O7" s="20"/>
-      <c r="P7" s="20"/>
-      <c r="Q7" s="20"/>
-      <c r="R7" s="20"/>
-      <c r="S7" s="20"/>
-      <c r="T7" s="20"/>
-      <c r="U7" s="20"/>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="A8" s="23"/>
-      <c r="B8" s="20"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="13"/>
+      <c r="S7" s="13"/>
+      <c r="T7" s="13"/>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="A8" s="15"/>
+      <c r="B8" s="13"/>
       <c r="C8" s="8"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
       <c r="I8" s="9"/>
-      <c r="J8" s="23"/>
-      <c r="K8" s="20"/>
-      <c r="L8" s="20"/>
-      <c r="M8" s="20"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="20"/>
-      <c r="P8" s="20"/>
-      <c r="Q8" s="20"/>
-      <c r="R8" s="20"/>
-      <c r="S8" s="20"/>
-      <c r="T8" s="20"/>
-      <c r="U8" s="20"/>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="A9" s="23"/>
-      <c r="B9" s="20"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="13"/>
+      <c r="S8" s="13"/>
+      <c r="T8" s="13"/>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="A9" s="15"/>
+      <c r="B9" s="13"/>
       <c r="C9" s="8"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="20"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
       <c r="I9" s="9"/>
-      <c r="J9" s="23"/>
-      <c r="K9" s="20"/>
-      <c r="L9" s="20"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="23"/>
-      <c r="O9" s="20"/>
-      <c r="P9" s="20"/>
-      <c r="Q9" s="20"/>
-      <c r="R9" s="20"/>
-      <c r="S9" s="20"/>
-      <c r="T9" s="20"/>
-      <c r="U9" s="20"/>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.4">
-      <c r="A10" s="23"/>
-      <c r="B10" s="20"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="13"/>
+      <c r="S9" s="13"/>
+      <c r="T9" s="13"/>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="A10" s="15"/>
+      <c r="B10" s="13"/>
       <c r="C10" s="8"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
       <c r="I10" s="9"/>
-      <c r="J10" s="23"/>
-      <c r="K10" s="20"/>
-      <c r="L10" s="20"/>
-      <c r="M10" s="20"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="20"/>
-      <c r="P10" s="20"/>
-      <c r="Q10" s="20"/>
-      <c r="R10" s="20"/>
-      <c r="S10" s="20"/>
-      <c r="T10" s="20"/>
-      <c r="U10" s="20"/>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.4">
+      <c r="J10" s="15"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13"/>
+      <c r="S10" s="13"/>
+      <c r="T10" s="13"/>
+    </row>
+    <row r="11" spans="1:20">
       <c r="I11" s="9"/>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:20">
       <c r="I12" s="9"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:20">
       <c r="I13" s="9"/>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:20">
       <c r="I14" s="9"/>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:20">
       <c r="I15" s="9"/>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:20">
       <c r="I16" s="9"/>
     </row>
-    <row r="17" spans="9:9" x14ac:dyDescent="0.4">
+    <row r="17" spans="9:9">
       <c r="I17" s="9"/>
     </row>
-    <row r="18" spans="9:9" x14ac:dyDescent="0.4">
+    <row r="18" spans="9:9">
       <c r="I18" s="9"/>
     </row>
-    <row r="19" spans="9:9" x14ac:dyDescent="0.4">
+    <row r="19" spans="9:9">
       <c r="I19" s="9"/>
     </row>
-    <row r="20" spans="9:9" x14ac:dyDescent="0.4">
+    <row r="20" spans="9:9">
       <c r="I20" s="9"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7"/>
-  <dataValidations count="4">
-    <dataValidation type="list" sqref="C2:C10 L2:L10" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <phoneticPr fontId="4"/>
+  <dataValidations count="7">
+    <dataValidation type="list" sqref="L3:L10 C3:C10" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"clinic,night,map"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E2:E10 G2:G10" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" sqref="E3:E10 G3:G10" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"gte,lte"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="K2:K10" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>"cured,failed"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M2:M10 T2:T10" xr:uid="{00000000-0002-0000-0000-000005000000}">
+    <dataValidation type="list" sqref="S2:S10" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="L2" xr:uid="{CB93CAC9-E05A-42CD-BF51-C2A084B5D84B}">
+      <formula1>"clinic,night,end_game"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="E2 G2" xr:uid="{EEAB203E-6BC2-440A-AE17-A1B685A828E0}">
+      <formula1>"≥,≤"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="C2" xr:uid="{6ECE54C8-5545-4B8F-B19D-F059532E0477}">
+      <formula1>"clinic,night,night_end"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -937,7 +934,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="11.25" style="4" customWidth="1"/>
     <col min="2" max="2" width="10.5" style="4" customWidth="1"/>
@@ -950,7 +947,7 @@
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -976,7 +973,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -996,7 +993,7 @@
       </c>
       <c r="H2" s="1"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1016,7 +1013,7 @@
       </c>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1034,7 +1031,7 @@
       <c r="G4" s="2"/>
       <c r="H4" s="1"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1048,7 +1045,7 @@
       <c r="G5" s="2"/>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1060,7 +1057,7 @@
       <c r="G6" s="2"/>
       <c r="H6" s="1"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -1071,7 +1068,7 @@
       <c r="H7" s="3"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7"/>
+  <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/DataTables/DetailText/剧情/aaa模板.xlsx
+++ b/DataTables/DetailText/剧情/aaa模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A76BB6F-0DAC-40E8-8DFF-C3DF6BD9FC7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C23F4A3-1963-45E5-BE55-3483AF23D02A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="14566" windowHeight="15563" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-83" yWindow="0" windowWidth="7823" windowHeight="15563" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -305,7 +305,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -334,15 +334,6 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -355,9 +346,6 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -380,6 +368,15 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -612,265 +609,265 @@
     <col min="20" max="20" width="9.5625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="25" customFormat="1">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:20" s="21" customFormat="1">
+      <c r="A1" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="H1" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="18" t="s">
+      <c r="I1" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="J1" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="K1" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="L1" s="23" t="s">
+      <c r="L1" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="M1" s="19" t="s">
+      <c r="M1" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="N1" s="19" t="s">
+      <c r="N1" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="O1" s="19" t="s">
+      <c r="O1" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="P1" s="19" t="s">
+      <c r="P1" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="Q1" s="19" t="s">
+      <c r="Q1" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="R1" s="19" t="s">
+      <c r="R1" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="S1" s="24" t="s">
+      <c r="S1" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="24" t="s">
+      <c r="T1" s="20" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20">
-      <c r="A2" s="11"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="10"/>
-      <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-      <c r="Q2" s="10"/>
-      <c r="R2" s="17"/>
-      <c r="S2" s="17"/>
-      <c r="T2" s="17"/>
+    <row r="2" spans="1:20" s="21" customFormat="1">
+      <c r="A2" s="22"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="22"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="24"/>
+      <c r="S2" s="24"/>
+      <c r="T2" s="24"/>
     </row>
     <row r="3" spans="1:20">
-      <c r="A3" s="15"/>
-      <c r="B3" s="13"/>
+      <c r="A3" s="12"/>
+      <c r="B3" s="10"/>
       <c r="C3" s="8"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
       <c r="I3" s="9"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="16"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13"/>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
-      <c r="S3" s="13"/>
-      <c r="T3" s="13"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="11"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="10"/>
     </row>
     <row r="4" spans="1:20">
-      <c r="A4" s="15"/>
-      <c r="B4" s="13"/>
+      <c r="A4" s="12"/>
+      <c r="B4" s="10"/>
       <c r="C4" s="8"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
       <c r="I4" s="9"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="13"/>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="13"/>
-      <c r="R4" s="13"/>
-      <c r="S4" s="13"/>
-      <c r="T4" s="13"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="10"/>
+      <c r="T4" s="10"/>
     </row>
     <row r="5" spans="1:20">
-      <c r="A5" s="15"/>
-      <c r="B5" s="13"/>
+      <c r="A5" s="12"/>
+      <c r="B5" s="10"/>
       <c r="C5" s="8"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
       <c r="I5" s="9"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13"/>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="13"/>
-      <c r="R5" s="13"/>
-      <c r="S5" s="13"/>
-      <c r="T5" s="13"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="10"/>
+      <c r="S5" s="10"/>
+      <c r="T5" s="10"/>
     </row>
     <row r="6" spans="1:20">
-      <c r="A6" s="15"/>
-      <c r="B6" s="13"/>
+      <c r="A6" s="12"/>
+      <c r="B6" s="10"/>
       <c r="C6" s="8"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
       <c r="I6" s="9"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="13"/>
-      <c r="R6" s="13"/>
-      <c r="S6" s="13"/>
-      <c r="T6" s="13"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="10"/>
+      <c r="S6" s="10"/>
+      <c r="T6" s="10"/>
     </row>
     <row r="7" spans="1:20">
-      <c r="A7" s="15"/>
-      <c r="B7" s="13"/>
+      <c r="A7" s="12"/>
+      <c r="B7" s="10"/>
       <c r="C7" s="8"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
       <c r="I7" s="9"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
-      <c r="R7" s="13"/>
-      <c r="S7" s="13"/>
-      <c r="T7" s="13"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10"/>
+      <c r="S7" s="10"/>
+      <c r="T7" s="10"/>
     </row>
     <row r="8" spans="1:20">
-      <c r="A8" s="15"/>
-      <c r="B8" s="13"/>
+      <c r="A8" s="12"/>
+      <c r="B8" s="10"/>
       <c r="C8" s="8"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
       <c r="I8" s="9"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
-      <c r="P8" s="13"/>
-      <c r="Q8" s="13"/>
-      <c r="R8" s="13"/>
-      <c r="S8" s="13"/>
-      <c r="T8" s="13"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="10"/>
+      <c r="S8" s="10"/>
+      <c r="T8" s="10"/>
     </row>
     <row r="9" spans="1:20">
-      <c r="A9" s="15"/>
-      <c r="B9" s="13"/>
+      <c r="A9" s="12"/>
+      <c r="B9" s="10"/>
       <c r="C9" s="8"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
       <c r="I9" s="9"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="13"/>
-      <c r="R9" s="13"/>
-      <c r="S9" s="13"/>
-      <c r="T9" s="13"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="10"/>
+      <c r="S9" s="10"/>
+      <c r="T9" s="10"/>
     </row>
     <row r="10" spans="1:20">
-      <c r="A10" s="15"/>
-      <c r="B10" s="13"/>
+      <c r="A10" s="12"/>
+      <c r="B10" s="10"/>
       <c r="C10" s="8"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
       <c r="I10" s="9"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="13"/>
-      <c r="O10" s="13"/>
-      <c r="P10" s="13"/>
-      <c r="Q10" s="13"/>
-      <c r="R10" s="13"/>
-      <c r="S10" s="13"/>
-      <c r="T10" s="13"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="12"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
+      <c r="S10" s="10"/>
+      <c r="T10" s="10"/>
     </row>
     <row r="11" spans="1:20">
       <c r="I11" s="9"/>

--- a/DataTables/DetailText/剧情/aaa模板.xlsx
+++ b/DataTables/DetailText/剧情/aaa模板.xlsx
@@ -1,22 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C23F4A3-1963-45E5-BE55-3483AF23D02A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FC0534F-66B9-4413-BEA6-5929A9532511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="7823" windowHeight="15563" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
     <sheet name="StoryLine" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -379,7 +392,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -590,26 +603,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="6.6875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.5625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.0625" customWidth="1"/>
+    <col min="4" max="4" width="9.125" customWidth="1"/>
     <col min="5" max="8" width="8.375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8.375" style="4" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.9375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.9375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="28.75" customWidth="1"/>
+    <col min="14" max="14" width="8" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="26.75" customWidth="1"/>
     <col min="16" max="18" width="8.375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9.4375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.5625" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="21" customFormat="1">
+    <row r="1" spans="1:20" s="21" customFormat="1" ht="36">
       <c r="A1" s="16" t="s">
         <v>20</v>
       </c>
@@ -671,7 +683,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="21" customFormat="1">
+    <row r="2" spans="1:20" s="21" customFormat="1" ht="18">
       <c r="A2" s="22"/>
       <c r="B2" s="23"/>
       <c r="C2" s="23"/>

--- a/DataTables/DetailText/剧情/aaa模板.xlsx
+++ b/DataTables/DetailText/剧情/aaa模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FC0534F-66B9-4413-BEA6-5929A9532511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EAA24C6-AFA1-4E16-8150-08FA2EDB8B82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -621,7 +621,7 @@
     <col min="19" max="20" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="21" customFormat="1" ht="36">
+    <row r="1" spans="1:20" s="21" customFormat="1" ht="18">
       <c r="A1" s="16" t="s">
         <v>20</v>
       </c>
@@ -927,7 +927,7 @@
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="L2" xr:uid="{CB93CAC9-E05A-42CD-BF51-C2A084B5D84B}">
-      <formula1>"clinic,night,end_game"</formula1>
+      <formula1>"clinic,night,endgame"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="E2 G2" xr:uid="{EEAB203E-6BC2-440A-AE17-A1B685A828E0}">
       <formula1>"≥,≤"</formula1>

--- a/DataTables/DetailText/剧情/aaa模板.xlsx
+++ b/DataTables/DetailText/剧情/aaa模板.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EAA24C6-AFA1-4E16-8150-08FA2EDB8B82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6BE5BFB-DA3E-4396-B347-8B8E10B1C23F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -392,7 +392,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -603,7 +603,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="6.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.625" bestFit="1" customWidth="1"/>
@@ -621,7 +621,7 @@
     <col min="19" max="20" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="21" customFormat="1" ht="18">
+    <row r="1" spans="1:20" s="21" customFormat="1">
       <c r="A1" s="16" t="s">
         <v>20</v>
       </c>
@@ -683,7 +683,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="21" customFormat="1" ht="18">
+    <row r="2" spans="1:20" s="21" customFormat="1">
       <c r="A2" s="22"/>
       <c r="B2" s="23"/>
       <c r="C2" s="23"/>
@@ -927,7 +927,7 @@
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="L2" xr:uid="{CB93CAC9-E05A-42CD-BF51-C2A084B5D84B}">
-      <formula1>"clinic,night,endgame"</formula1>
+      <formula1>"clinic,night,gameover,endgame"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="E2 G2" xr:uid="{EEAB203E-6BC2-440A-AE17-A1B685A828E0}">
       <formula1>"≥,≤"</formula1>

--- a/DataTables/DetailText/剧情/aaa模板.xlsx
+++ b/DataTables/DetailText/剧情/aaa模板.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6BE5BFB-DA3E-4396-B347-8B8E10B1C23F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04741DD7-D42B-4F70-83E8-78C20B8CFD5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="39">
   <si>
     <t>LineIndex</t>
   </si>
@@ -178,6 +178,10 @@
   </si>
   <si>
     <t>播放后</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Music</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -392,7 +396,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -603,7 +607,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="6.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.625" bestFit="1" customWidth="1"/>
@@ -621,7 +625,7 @@
     <col min="19" max="20" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="21" customFormat="1">
+    <row r="1" spans="1:20" s="21" customFormat="1" ht="18">
       <c r="A1" s="16" t="s">
         <v>20</v>
       </c>
@@ -683,7 +687,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="21" customFormat="1">
+    <row r="2" spans="1:20" s="21" customFormat="1" ht="18">
       <c r="A2" s="22"/>
       <c r="B2" s="23"/>
       <c r="C2" s="23"/>
@@ -942,7 +946,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="11.25" style="4" customWidth="1"/>
@@ -956,7 +960,7 @@
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -981,8 +985,11 @@
       <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1001,8 +1008,9 @@
         <v>11</v>
       </c>
       <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1021,8 +1029,9 @@
         <v>15</v>
       </c>
       <c r="H3" s="1"/>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1039,8 +1048,9 @@
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="1"/>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1053,8 +1063,9 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="1"/>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1065,8 +1076,9 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="1"/>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -1075,6 +1087,7 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4"/>
